--- a/models/sovereigns/Benin_Sovereign_Model.xlsx
+++ b/models/sovereigns/Benin_Sovereign_Model.xlsx
@@ -957,16 +957,34 @@
           <t>fdi_net_pct_gdp</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
+      <c r="B15" s="2" t="n">
+        <v>1.961</v>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>World Bank WDI</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1076,16 +1094,34 @@
           <t>nominal_gdp_usd_bn</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n"/>
+      <c r="B22" s="2" t="n">
+        <v>27.786</v>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>USD bn</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/models/sovereigns/Benin_Sovereign_Model.xlsx
+++ b/models/sovereigns/Benin_Sovereign_Model.xlsx
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026E</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IMF</t>
+          <t>IMF / Ministry of Economy and Finance</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>central government public debt (~60.5% incl SOEs)</t>
+          <t>central government debt (about 60.5% including SOE liabilities under IMF perimeter)</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>IMF</t>
+          <t>IMF (tax revenue)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1301,16 +1301,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Blended 42-month EFF/ECF ($638m) and RSF ($200m) completed 25-Feb-26</t>
+          <t>EFF/ECF/RSF (42-month blended) completed</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>0.838</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>08-Jul-22</t>
-        </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1477,7 +1472,7 @@
       <c r="D8" s="2" t="n"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IMF, 25-Feb-26</t>
+          <t>IMF / Ministry of Economy and Finance, 25-Feb-26</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1511,7 @@
       <c r="D11" s="2" t="n"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>IMF, 25-Feb-26</t>
+          <t>IMF, 25-Feb-26 (tax revenue)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Benin_Sovereign_Model.xlsx
+++ b/models/sovereigns/Benin_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 08-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/benin.json</t>
+          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/benin.json</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IMF / Ministry of Economy and Finance</t>
+          <t>IMF</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>central government debt (about 60.5% including SOE liabilities under IMF perimeter)</t>
+          <t>Central government debt; ~60.5% incl. SOE liabilities under IMF perimeter</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EFF/ECF/RSF (42-month blended) completed</t>
+          <t>EFF/ECF/RSF (42-month blended) completed; final disbursement USD 118m</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1472,7 +1472,7 @@
       <c r="D8" s="2" t="n"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IMF / Ministry of Economy and Finance, 25-Feb-26</t>
+          <t>IMF, 25-Feb-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Benin_Sovereign_Model.xlsx
+++ b/models/sovereigns/Benin_Sovereign_Model.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>as of 08-Oct-26</t>
+          <t>as of 09-Oct-26</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Central government debt; ~60.5% incl. SOE liabilities under IMF perimeter</t>
+          <t>Central government debt, excl. SOE liabilities (about 60.5% incl. SOEs)</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>latest</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EFF/ECF/RSF (42-month blended) completed; final disbursement USD 118m</t>
+          <t>Blended EFF/ECF (USD 638m) and RSF (USD 200m), 42 months, completed; no active programme</t>
         </is>
       </c>
       <c r="C33" t="n">

--- a/models/sovereigns/Benin_Sovereign_Model.xlsx
+++ b/models/sovereigns/Benin_Sovereign_Model.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Central government debt, excl. SOE liabilities (about 60.5% incl. SOEs)</t>
+          <t>central government debt; ~60.5% including SOE liabilities under IMF perimeter</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>latest</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Blended EFF/ECF (USD 638m) and RSF (USD 200m), 42 months, completed; no active programme</t>
+          <t>Blended 42-month EFF/ECF and RSF arrangements, completed 25-Feb-26 (final tranche USD 118m)</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1324,7 +1324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1348,10 +1348,15 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>2026E</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -1366,7 +1371,8 @@
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="n"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1378,10 +1384,11 @@
       <c r="C3" s="2" t="n">
         <v>7.5</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n">
         <v>6.5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>INSAE / IMF, 25-Feb-26</t>
         </is>
@@ -1397,10 +1404,11 @@
       <c r="C4" s="2" t="n">
         <v>1.25</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n">
         <v>1.25</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>BCEAO / INSAE, 15-Aug-26</t>
         </is>
@@ -1417,7 +1425,8 @@
         <v>-5.5</v>
       </c>
       <c r="D5" s="2" t="n"/>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" t="inlineStr">
         <is>
           <t>IMF, 25-Feb-26</t>
         </is>
@@ -1436,7 +1445,8 @@
         <v>-2.8</v>
       </c>
       <c r="D6" s="2" t="n"/>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Ministry of Economy and Finance / IMF, 25-Feb-26</t>
         </is>
@@ -1453,7 +1463,8 @@
         <v>-0.6</v>
       </c>
       <c r="D7" s="2" t="n"/>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" t="inlineStr">
         <is>
           <t>IMF, 25-Feb-26</t>
         </is>
@@ -1470,7 +1481,8 @@
         <v>54</v>
       </c>
       <c r="D8" s="2" t="n"/>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" t="inlineStr">
         <is>
           <t>IMF, 25-Feb-26</t>
         </is>
@@ -1485,7 +1497,8 @@
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1496,7 +1509,8 @@
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1509,7 +1523,8 @@
         <v>14.5</v>
       </c>
       <c r="D11" s="2" t="n"/>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" t="inlineStr">
         <is>
           <t>IMF, 25-Feb-26 (tax revenue)</t>
         </is>
@@ -1525,8 +1540,11 @@
       <c r="C12" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" t="inlineStr">
+      <c r="D12" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" t="inlineStr">
         <is>
           <t>Moody's, 14-Aug-26</t>
         </is>

--- a/models/sovereigns/Benin_Sovereign_Model.xlsx
+++ b/models/sovereigns/Benin_Sovereign_Model.xlsx
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>latest (period not stated)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>central government debt; ~60.5% including SOE liabilities under IMF perimeter</t>
+          <t>central government debt (about 60.5% including SOE liabilities under IMF perimeter)</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>latest (period not stated)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>latest (period not stated)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Blended 42-month EFF/ECF and RSF arrangements, completed 25-Feb-26 (final tranche USD 118m)</t>
+          <t>EFF/ECF (42-month, blended) and RSF arrangements, completed</t>
         </is>
       </c>
       <c r="C33" t="n">

--- a/models/sovereigns/Benin_Sovereign_Model.xlsx
+++ b/models/sovereigns/Benin_Sovereign_Model.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>INSAE / IMF</t>
+          <t>INSAE / IMF Executive Board Press Release No. 26/54</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>latest (period not stated)</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IMF</t>
+          <t>IMF Executive Board Press Release No. 26/54</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>central government debt (about 60.5% including SOE liabilities under IMF perimeter)</t>
+          <t>central government debt (about 60.5% including SOE liabilities on the IMF perimeter)</t>
         </is>
       </c>
     </row>
@@ -795,12 +795,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>latest (period not stated)</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>IMF</t>
+          <t>IMF Executive Board Press Release No. 26/54</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>latest (period not stated)</t>
+          <t>latest</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Moody's Ratings, Benin upgraded to Ba3</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IMF</t>
+          <t>IMF Executive Board Press Release No. 26/54</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EFF/ECF (42-month, blended) and RSF arrangements, completed</t>
+          <t>42-month blended EFF/ECF and RSF arrangements, completed (final review)</t>
         </is>
       </c>
       <c r="C33" t="n">

--- a/models/sovereigns/Benin_Sovereign_Model.xlsx
+++ b/models/sovereigns/Benin_Sovereign_Model.xlsx
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -712,12 +712,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026E</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>INSAE / IMF Executive Board Press Release No. 26/54</t>
+          <t>INSAE / IMF</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>latest per IMF 25-Feb-26</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IMF Executive Board Press Release No. 26/54</t>
+          <t>IMF</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>central government debt (about 60.5% including SOE liabilities on the IMF perimeter)</t>
+          <t>Central government debt (about 60.5% incl. SOE liabilities under IMF perimeter)</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>IMF Executive Board Press Release No. 26/54</t>
+          <t>IMF</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>latest</t>
+          <t>latest per Moody's 14-Aug-26</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Moody's Ratings, Benin upgraded to Ba3</t>
+          <t>Moody's Ratings</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IMF Executive Board Press Release No. 26/54</t>
+          <t>IMF</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>42-month blended EFF/ECF and RSF arrangements, completed (final review)</t>
+          <t>Blended EFF/ECF and RSF arrangements (42 months), completed with final review</t>
         </is>
       </c>
       <c r="C33" t="n">

--- a/models/sovereigns/Benin_Sovereign_Model.xlsx
+++ b/models/sovereigns/Benin_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/benin.json</t>
+          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/benin.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Benin_Sovereign_Model.xlsx
+++ b/models/sovereigns/Benin_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/benin.json</t>
+          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/benin.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Benin_Sovereign_Model.xlsx
+++ b/models/sovereigns/Benin_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/benin.json</t>
+          <t>built 26-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/benin.json</t>
         </is>
       </c>
     </row>
